--- a/InputData/indst/_cement/CUUB/Cement Utilization Upper Bound.xlsx
+++ b/InputData/indst/_cement/CUUB/Cement Utilization Upper Bound.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CUUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB556E0-B7FB-4E18-A746-EADD09CA60BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B47D01A-788B-412D-BD5A-DEA4551254BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -475,50 +475,50 @@
     <t>Purpose and layout</t>
   </si>
   <si>
-    <t>This file gives the upper bound of the region's historical clinker-capacity utilization range. Utilization here is the clinker the region needs to make divided by the clinker capacity the fleet has at the start of the year. EPS turns it into a 'fleet tightness' index: (utilization - CULB) / (CUUB - CULB), held between 0 and 1. Zero means the fleet is at the bottom of its historical range (chronic overcapacity, so a retiring kiln's output can be absorbed by the rest of the fleet); one means it is at the top (a tight market that needs new capacity). The tightness index feeds the replacement blend weight (CRBW) and the congestion adder (CTOA), which shape the decision to overhaul or replace a kiln. The upper bound also sets the production ceiling: when demand outpaces capacity, existing kilns can run up to this utilization. Starting utilization (SYCCU) remains the basis for initialization and for sizing new builds.
+    <t>Using it for other regions</t>
+  </si>
+  <si>
+    <t>We set this file up to be adaptable to each of the main EPS regions. If you are working on a non-US region, use the drop-down selector at the top of the 'Regions' tab to choose a different country, and the 'CUUB' tab updates on its own; just re-export the CSV. The Confidence column says how far to trust each row, and rows marked PROXY are placeholders borrowed from the U.S. pattern with no observed value behind them. Replace those before relying on a regional run. The bounds are not strictly comparable between regions, because some are measured against clinker capacity and some against cement capacity (see the Basis column).</t>
+  </si>
+  <si>
+    <t>U.S. value</t>
+  </si>
+  <si>
+    <t>Other regions' values</t>
+  </si>
+  <si>
+    <t>Starting values come from national associations, trade press, and our own arithmetic, listed under Sources. Confidence is rated HIGH (Brazil and the U.S.), MEDIUM (India and Indonesia), LOW-MED (China and the EU), LOW (Canada, Mexico, and Australia), or NONE (Japan). Indonesia's 0.93 (2012) is well attested, and India's 0.88 (2007) rests on weak evidence. Brazil's 0.85 comes from its explicit series. China, the EU, Japan, Mexico, Canada, and Australia are placeholders; Australia's 0.90 reflects kilns that run full or not at all. The 'Regions' tab notes give the details. Unlike BCD, these rows do not use the DIRECT/SNIPPET/JUDGMENT tags; where a figure came from a search summary rather than the document, the note says so.</t>
+  </si>
+  <si>
+    <t>Pick a region from the drop-down in B1. The Derivation and the export tab update on their own; re-export the CSV afterward. A blank cell means no sourced value yet.</t>
+  </si>
+  <si>
+    <t>Original research table for all regions, kept for reference (the Derivation does not read it). Figures come from secondary citations of primary sources; check the primary document before use.</t>
+  </si>
+  <si>
+    <t>2024 trough=property collapse + chronic overcapacity; NO verified historical peak - 0.85 is a PROXY pending CCA/NBS archives; clinker vs cement rates differ; registered-vs-operable gap (32.5 ban, capacity swaps) | CCA capacity 1,810 Mt + 53% utilization 2024 (SNIPPET, Global Cement) supports the 0.50 trough; still unclear if clinker or cement basis. GEM 2026 operating clinker capacity 1,636.9 Mt (DIRECT, GEM article); clinker output not found, so utilization on the GEM base is unknown.</t>
+  </si>
+  <si>
+    <t>FY2021 COVID trough; 0.88=Aug-2007 CMA point cited in a 2008 article (weak); recent 0.71-0.75 range | GEM 2026 clinker capacity 402.5 Mt (DIRECT, GEM article); implied clinker utilization ~0.77 (= 0.73 x 427 / 402.5, JUDGMENT) - inside the band, but the band is cement basis (CMA).</t>
+  </si>
+  <si>
+    <t>explicit 2007-2023 series; trough=2015-18 domestic recession not 2008-09; 2023 value ambiguous in extraction (0.67-0.76) - use 2022 | SNIC cement capacity 94 Mt/yr (DIRECT); chart prints 0.76 for 2023 vs 66.5/94 = 0.71 (JUDGMENT) - check chart definition; clinker basis ~47/61 = 0.77 (JUDGMENT, USGS capacity).</t>
+  </si>
+  <si>
+    <t>NO utilization series found; staged band is a US-analog PROXY; CANACEM 39.6Mt capacity vs 51.5Mt 2021 production are different vintages - do not combine | one-point check only - implied clinker ~33 Mt (0.75 x 44, 2016 ratio, JUDGMENT) / USGS clinker capacity 42 = ~0.79; utilization series still TO FILL.</t>
+  </si>
+  <si>
+    <t>0.929 peak 2012 well-attested; recent estimates 0.56 vs 0.65 disagree (installed vs operable denominator); post-2015 capacity glut | ASI projects 0.65 for 2025 (SNIPPET, Global Cement); clinker basis 57.3 / 83 (USGS capacity) = 0.69 (JUDGMENT).</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>This file gives the upper bound of the region's historical clinker-capacity utilization range. Utilization here is the clinker the region needs to make divided by the clinker capacity the fleet has at the start of the year. EPS turns it into a 'fleet tightness' index: (utilization - CULB) / (CUUB - CULB), held between 0 and 1. Zero means the fleet is at the bottom of its historical range (chronic overcapacity, so a retiring kiln's output can be absorbed by the rest of the fleet); one means it is at the top (a tight market that needs new capacity). The tightness index feeds the replacement blend weight (CRBW), which shapes the decision to overhaul or replace a kiln. The upper bound also sets the production ceiling: when demand outpaces capacity, existing kilns can run up to this utilization. Starting utilization (SYCCU) remains the basis for initialization and for sizing new builds.
 The tabs are 'Regions' (selector, each region's value, year, confidence, basis, and source), 'Regional anchors master' (the original research table for all regions, kept for reference; the Derivation does not read it), 'Derivation' (picks the selected region's row), and 'Checks' (simple range checks). The last tab, 'CUUB', reads the Derivation and is what gets exported to CUUB.csv.</t>
   </si>
   <si>
-    <t>Using it for other regions</t>
-  </si>
-  <si>
-    <t>We set this file up to be adaptable to each of the main EPS regions. If you are working on a non-US region, use the drop-down selector at the top of the 'Regions' tab to choose a different country, and the 'CUUB' tab updates on its own; just re-export the CSV. The Confidence column says how far to trust each row, and rows marked PROXY are placeholders borrowed from the U.S. pattern with no observed value behind them. Replace those before relying on a regional run. The bounds are not strictly comparable between regions, because some are measured against clinker capacity and some against cement capacity (see the Basis column).</t>
-  </si>
-  <si>
-    <t>U.S. value</t>
-  </si>
-  <si>
-    <t>For the U.S. national file version we use 0.85, the 2005 peak of 'full practicable capacity', on a clinker basis. We use the widest range the historical record supports (the deepest trough and highest peak) rather than a narrower 'normal operations' band, so the shape of the CRBW and CTOA curves, not the band edge, decides where pressure on the fleet gets strong. The 2025 U.S. utilization of 0.69 sits near the middle, at a tightness of about 0.56.</t>
-  </si>
-  <si>
-    <t>Other regions' values</t>
-  </si>
-  <si>
-    <t>Starting values come from national associations, trade press, and our own arithmetic, listed under Sources. Confidence is rated HIGH (Brazil and the U.S.), MEDIUM (India and Indonesia), LOW-MED (China and the EU), LOW (Canada, Mexico, and Australia), or NONE (Japan). Indonesia's 0.93 (2012) is well attested, and India's 0.88 (2007) rests on weak evidence. Brazil's 0.85 comes from its explicit series. China, the EU, Japan, Mexico, Canada, and Australia are placeholders; Australia's 0.90 reflects kilns that run full or not at all. The 'Regions' tab notes give the details. Unlike BCD, these rows do not use the DIRECT/SNIPPET/JUDGMENT tags; where a figure came from a search summary rather than the document, the note says so.</t>
-  </si>
-  <si>
-    <t>Pick a region from the drop-down in B1. The Derivation and the export tab update on their own; re-export the CSV afterward. A blank cell means no sourced value yet.</t>
-  </si>
-  <si>
-    <t>Original research table for all regions, kept for reference (the Derivation does not read it). Figures come from secondary citations of primary sources; check the primary document before use.</t>
-  </si>
-  <si>
-    <t>2024 trough=property collapse + chronic overcapacity; NO verified historical peak - 0.85 is a PROXY pending CCA/NBS archives; clinker vs cement rates differ; registered-vs-operable gap (32.5 ban, capacity swaps) | CCA capacity 1,810 Mt + 53% utilization 2024 (SNIPPET, Global Cement) supports the 0.50 trough; still unclear if clinker or cement basis. GEM 2026 operating clinker capacity 1,636.9 Mt (DIRECT, GEM article); clinker output not found, so utilization on the GEM base is unknown.</t>
-  </si>
-  <si>
-    <t>FY2021 COVID trough; 0.88=Aug-2007 CMA point cited in a 2008 article (weak); recent 0.71-0.75 range | GEM 2026 clinker capacity 402.5 Mt (DIRECT, GEM article); implied clinker utilization ~0.77 (= 0.73 x 427 / 402.5, JUDGMENT) - inside the band, but the band is cement basis (CMA).</t>
-  </si>
-  <si>
-    <t>explicit 2007-2023 series; trough=2015-18 domestic recession not 2008-09; 2023 value ambiguous in extraction (0.67-0.76) - use 2022 | SNIC cement capacity 94 Mt/yr (DIRECT); chart prints 0.76 for 2023 vs 66.5/94 = 0.71 (JUDGMENT) - check chart definition; clinker basis ~47/61 = 0.77 (JUDGMENT, USGS capacity).</t>
-  </si>
-  <si>
-    <t>NO utilization series found; staged band is a US-analog PROXY; CANACEM 39.6Mt capacity vs 51.5Mt 2021 production are different vintages - do not combine | one-point check only - implied clinker ~33 Mt (0.75 x 44, 2016 ratio, JUDGMENT) / USGS clinker capacity 42 = ~0.79; utilization series still TO FILL.</t>
-  </si>
-  <si>
-    <t>0.929 peak 2012 well-attested; recent estimates 0.56 vs 0.65 disagree (installed vs operable denominator); post-2015 capacity glut | ASI projects 0.65 for 2025 (SNIPPET, Global Cement); clinker basis 57.3 / 83 (USGS capacity) = 0.69 (JUDGMENT).</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless</t>
+    <t>For the U.S. national file version we use 0.85, the 2005 peak of 'full practicable capacity', on a clinker basis. We use the widest range the historical record supports (the deepest trough and highest peak) rather than a narrower 'normal operations' band, so the shape of the CRBW curve, not the band edge, decides where pressure on the fleet gets strong. The 2025 U.S. utilization of 0.69 sits near the middle, at a tightness of about 0.56.</t>
   </si>
 </sst>
 </file>
@@ -598,7 +598,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -619,6 +619,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -925,20 +928,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="110.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="110.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -949,45 +952,45 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>86</v>
       </c>
@@ -995,31 +998,31 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="10" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="10">
         <v>2026</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="10">
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B14" s="9" t="s">
         <v>88</v>
       </c>
@@ -1027,15 +1030,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="8" t="s">
         <v>38</v>
       </c>
@@ -1043,31 +1046,31 @@
         <v>123</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="10">
         <v>2024</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="10">
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="9" t="s">
         <v>92</v>
       </c>
@@ -1075,15 +1078,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="8" t="s">
         <v>19</v>
       </c>
@@ -1091,29 +1094,29 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="10" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" s="10">
         <v>2025</v>
       </c>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="9" t="s">
         <v>96</v>
       </c>
@@ -1121,15 +1124,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="2:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="B29" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="10" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="8" t="s">
         <v>98</v>
       </c>
@@ -1137,47 +1140,47 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B32" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="10" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="10" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="2">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="10">
         <v>2026</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="10">
         <v>2017</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="10" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="8" t="s">
         <v>24</v>
       </c>
@@ -1185,43 +1188,43 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="10" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="2"/>
-      <c r="D41" s="2"/>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="10"/>
+      <c r="D41" s="10"/>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="10" t="s">
         <v>105</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B43" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="10" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B45" s="8" t="s">
         <v>107</v>
       </c>
@@ -1229,29 +1232,29 @@
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="10" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="2">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="10">
         <v>2026</v>
       </c>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B49" s="9" t="s">
         <v>110</v>
       </c>
@@ -1259,94 +1262,94 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="B50" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B52" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B53" s="10" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B54" s="10" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B55" s="10">
         <v>2021</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B56" s="10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
+    <row r="57" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B57" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="195" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="B62" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B62" s="2" t="s">
+    </row>
+    <row r="63" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="B63" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B64" s="10" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{8091F716-AA12-4F76-806E-0D536C21B9B8}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{DBEB8732-E4E1-4B0E-B75A-6519E351704B}"/>
-    <hyperlink ref="B21" r:id="rId3" xr:uid="{96AA6EE9-5D6F-4256-A2F3-667E933B617C}"/>
-    <hyperlink ref="B28" r:id="rId4" xr:uid="{5326C364-FD2A-4339-A949-3B7FFE12960E}"/>
-    <hyperlink ref="B35" r:id="rId5" xr:uid="{FE1D3049-2704-4064-A305-53A3EEF73B5B}"/>
-    <hyperlink ref="B49" r:id="rId6" xr:uid="{7212EC31-6F89-4C88-AE0B-D724952F2304}"/>
-    <hyperlink ref="D14" r:id="rId7" xr:uid="{59B7FD89-EEA1-487F-B4D9-D3647F21B818}"/>
-    <hyperlink ref="D21" r:id="rId8" xr:uid="{B2449EEC-7830-4EFD-A787-8AE56FB1665F}"/>
-    <hyperlink ref="D28" r:id="rId9" xr:uid="{C943D726-3B33-4B85-9042-75D2BF653313}"/>
-    <hyperlink ref="D42" r:id="rId10" xr:uid="{B7C543BF-4FAA-439A-A6AB-88971A3DCDF8}"/>
-    <hyperlink ref="D49" r:id="rId11" xr:uid="{580F20B4-917B-4B4F-8F00-5C3D7B71CF75}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{DB23B333-42A4-4AE0-8B04-3BF865AD80B3}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{F4D93CF1-4207-45C8-AF06-C493A4971F87}"/>
+    <hyperlink ref="B21" r:id="rId3" xr:uid="{46DA1831-05F2-4A25-A15B-4B391B9386B7}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{E2808A16-BF77-4463-B632-3A08B5860093}"/>
+    <hyperlink ref="B35" r:id="rId5" xr:uid="{B9F86986-E577-43A8-8ED8-8DCD6C629D7B}"/>
+    <hyperlink ref="B49" r:id="rId6" xr:uid="{F0AF8119-CAB1-4324-BC70-06BC7AE17EFC}"/>
+    <hyperlink ref="D14" r:id="rId7" xr:uid="{9927FE73-CD03-4D40-B4A7-A932F35A2ED8}"/>
+    <hyperlink ref="D21" r:id="rId8" xr:uid="{05331FF0-A5EC-4918-AF0E-17452FD25F11}"/>
+    <hyperlink ref="D28" r:id="rId9" xr:uid="{AE843CAB-6943-4AE0-A6B1-F2C0D95449CC}"/>
+    <hyperlink ref="D42" r:id="rId10" xr:uid="{8C3CDFC8-CCC6-4795-9511-B7356A0DD001}"/>
+    <hyperlink ref="D49" r:id="rId11" xr:uid="{4DF4942D-E01D-4A4D-B0AA-D1DA7D7EF906}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1355,7 +1358,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1366,7 +1369,7 @@
     <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1374,12 +1377,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1402,7 +1405,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1425,7 +1428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1445,10 +1448,10 @@
         <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1468,10 +1471,10 @@
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1494,7 +1497,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1537,10 +1540,10 @@
         <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1560,10 +1563,10 @@
         <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1586,7 +1589,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -1606,10 +1609,10 @@
         <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -1645,17 +1648,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1690,7 +1693,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -1725,7 +1728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1760,7 +1763,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1795,7 +1798,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -1830,7 +1833,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1865,7 +1868,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>74</v>
       </c>
@@ -1900,7 +1903,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1935,7 +1938,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1964,7 +1967,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1993,7 +1996,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -2036,12 +2039,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>76</v>
       </c>
@@ -2050,7 +2053,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2059,7 +2062,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>77</v>
       </c>
@@ -2076,18 +2079,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="70.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="70.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -2096,7 +2099,7 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -2116,17 +2119,17 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
